--- a/artfynd/A 58876-2025 artfynd.xlsx
+++ b/artfynd/A 58876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127011821</v>
       </c>
       <c r="B2" t="n">
-        <v>75144</v>
+        <v>75135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127011817</v>
       </c>
       <c r="B3" t="n">
-        <v>82861</v>
+        <v>82852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>127011819</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127011815</v>
+        <v>127011814</v>
       </c>
       <c r="B5" t="n">
-        <v>98367</v>
+        <v>80114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539372</v>
+        <v>539373</v>
       </c>
       <c r="R5" t="n">
-        <v>7022220</v>
+        <v>7022206</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127011814</v>
+        <v>127011815</v>
       </c>
       <c r="B6" t="n">
-        <v>80123</v>
+        <v>98353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539373</v>
+        <v>539372</v>
       </c>
       <c r="R6" t="n">
-        <v>7022206</v>
+        <v>7022220</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>127011823</v>
       </c>
       <c r="B7" t="n">
-        <v>91332</v>
+        <v>91319</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>127011820</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>91615</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127011818</v>
+        <v>127011816</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>91319</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539392</v>
+        <v>539368</v>
       </c>
       <c r="R9" t="n">
-        <v>7022267</v>
+        <v>7022234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127011822</v>
+        <v>127011818</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>80114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539391</v>
+        <v>539392</v>
       </c>
       <c r="R10" t="n">
-        <v>7022279</v>
+        <v>7022267</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127011816</v>
+        <v>127011822</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539368</v>
+        <v>539391</v>
       </c>
       <c r="R11" t="n">
-        <v>7022234</v>
+        <v>7022279</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
         <v>127011813</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>91337</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 58876-2025 artfynd.xlsx
+++ b/artfynd/A 58876-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127011821</v>
       </c>
       <c r="B2" t="n">
-        <v>75135</v>
+        <v>75144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127011817</v>
       </c>
       <c r="B3" t="n">
-        <v>82852</v>
+        <v>82861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>127011819</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -967,32 +967,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127011814</v>
+        <v>127011815</v>
       </c>
       <c r="B5" t="n">
-        <v>80114</v>
+        <v>98367</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539373</v>
+        <v>539372</v>
       </c>
       <c r="R5" t="n">
-        <v>7022206</v>
+        <v>7022220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1064,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127011815</v>
+        <v>127011814</v>
       </c>
       <c r="B6" t="n">
-        <v>98353</v>
+        <v>80123</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539372</v>
+        <v>539373</v>
       </c>
       <c r="R6" t="n">
-        <v>7022220</v>
+        <v>7022206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,7 +1164,7 @@
         <v>127011823</v>
       </c>
       <c r="B7" t="n">
-        <v>91319</v>
+        <v>91332</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>127011820</v>
       </c>
       <c r="B8" t="n">
-        <v>91615</v>
+        <v>91628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,10 +1355,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127011816</v>
+        <v>127011818</v>
       </c>
       <c r="B9" t="n">
-        <v>91319</v>
+        <v>80123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>539368</v>
+        <v>539392</v>
       </c>
       <c r="R9" t="n">
-        <v>7022234</v>
+        <v>7022267</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127011818</v>
+        <v>127011822</v>
       </c>
       <c r="B10" t="n">
-        <v>80114</v>
+        <v>79020</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1463,21 +1463,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539392</v>
+        <v>539391</v>
       </c>
       <c r="R10" t="n">
-        <v>7022267</v>
+        <v>7022279</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,10 +1549,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127011822</v>
+        <v>127011816</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>91332</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1560,21 +1560,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539391</v>
+        <v>539368</v>
       </c>
       <c r="R11" t="n">
-        <v>7022279</v>
+        <v>7022234</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
         <v>127011813</v>
       </c>
       <c r="B12" t="n">
-        <v>91337</v>
+        <v>91350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 58876-2025 artfynd.xlsx
+++ b/artfynd/A 58876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127011821</v>
+        <v>127011820</v>
       </c>
       <c r="B2" t="n">
-        <v>75144</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>539387</v>
+        <v>539389</v>
       </c>
       <c r="R2" t="n">
-        <v>7022285</v>
+        <v>7022278</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127011817</v>
+        <v>127011816</v>
       </c>
       <c r="B3" t="n">
-        <v>82861</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>539366</v>
+        <v>539368</v>
       </c>
       <c r="R3" t="n">
-        <v>7022250</v>
+        <v>7022234</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -851,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -870,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127011819</v>
+        <v>127011823</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -905,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>539384</v>
+        <v>539393</v>
       </c>
       <c r="R4" t="n">
-        <v>7022283</v>
+        <v>7022269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127011815</v>
+        <v>127011817</v>
       </c>
       <c r="B5" t="n">
-        <v>98367</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1002,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>539372</v>
+        <v>539366</v>
       </c>
       <c r="R5" t="n">
-        <v>7022220</v>
+        <v>7022250</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1046,6 +1045,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1064,32 +1064,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127011814</v>
+        <v>127011822</v>
       </c>
       <c r="B6" t="n">
-        <v>80123</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>539373</v>
+        <v>539391</v>
       </c>
       <c r="R6" t="n">
-        <v>7022206</v>
+        <v>7022279</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1161,10 +1161,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127011823</v>
+        <v>127011821</v>
       </c>
       <c r="B7" t="n">
-        <v>91332</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1172,21 +1172,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>539393</v>
+        <v>539387</v>
       </c>
       <c r="R7" t="n">
-        <v>7022269</v>
+        <v>7022285</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127011820</v>
+        <v>127011814</v>
       </c>
       <c r="B8" t="n">
-        <v>91628</v>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1269,21 +1269,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1293,10 +1293,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>539389</v>
+        <v>539373</v>
       </c>
       <c r="R8" t="n">
-        <v>7022278</v>
+        <v>7022206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1358,7 +1358,7 @@
         <v>127011818</v>
       </c>
       <c r="B9" t="n">
-        <v>80123</v>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1452,32 +1452,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127011822</v>
+        <v>127011815</v>
       </c>
       <c r="B10" t="n">
-        <v>79020</v>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1487,10 +1487,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>539391</v>
+        <v>539372</v>
       </c>
       <c r="R10" t="n">
-        <v>7022279</v>
+        <v>7022220</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1549,32 +1549,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127011816</v>
+        <v>127011819</v>
       </c>
       <c r="B11" t="n">
-        <v>91332</v>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>539368</v>
+        <v>539384</v>
       </c>
       <c r="R11" t="n">
-        <v>7022234</v>
+        <v>7022283</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,103 +1643,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>127011813</v>
-      </c>
-      <c r="B12" t="n">
-        <v>91350</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Boberg, Jmt</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>539382</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7022218</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Borgvattnet</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2025-07-27</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Clara Lerbro</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Clara Lerbro</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58876-2025 artfynd.xlsx
+++ b/artfynd/A 58876-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011820</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011816</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011823</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011817</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011822</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011814</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1449,6 +1489,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011818</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1546,6 +1591,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011815</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1643,8 +1693,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127011819</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>